--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3478,6 +3478,113 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123236979</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kullaskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>466750</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6322980</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Slätthög</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sonja Darell</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sonja Darell, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95911</v>
+        <v>95914</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95916</v>
+        <v>95922</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95922</v>
+        <v>95925</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95925</v>
+        <v>95942</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 44551-2020 artfynd.xlsx
+++ b/artfynd/A 44551-2020 artfynd.xlsx
@@ -3483,7 +3483,7 @@
         <v>123236979</v>
       </c>
       <c r="B24" t="n">
-        <v>95951</v>
+        <v>96332</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
